--- a/docs/Base de Datos de Masctoas.xlsx
+++ b/docs/Base de Datos de Masctoas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f5f906da8c23dd95/Desktop/Terremoto Mascotas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f5f906da8c23dd95/Desktop/Terremoto Mascotas/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2670" documentId="11_F25DC773A252ABDACC10485489D862385BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F70F2EC-F6BF-4EC0-A2E9-2E49A0FAAD8B}"/>
+  <xr:revisionPtr revIDLastSave="2677" documentId="11_F25DC773A252ABDACC10485489D862385BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B5F3749-DCAD-4793-B330-2E0232B75288}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Observadas" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2615" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2596" uniqueCount="665">
   <si>
     <t>ID</t>
   </si>
@@ -468,9 +468,6 @@
     <t>B70</t>
   </si>
   <si>
-    <t>B71</t>
-  </si>
-  <si>
     <t>B72</t>
   </si>
   <si>
@@ -1248,19 +1245,10 @@
     <t>Mascotas Desaparecidas Formulario 2</t>
   </si>
   <si>
-    <t>Renata</t>
-  </si>
-  <si>
     <t>Lucy</t>
   </si>
   <si>
     <t>Pitbull Terrier</t>
-  </si>
-  <si>
-    <t>Café Claro, Blanco</t>
-  </si>
-  <si>
-    <t>Torres del Limonar</t>
   </si>
   <si>
     <t>Orejas Caidas, patas un poco blancas</t>
@@ -2171,36 +2159,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2215,6 +2182,30 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2529,7 +2520,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F944E3DE-FE9C-4E6E-B46E-81628292EFC9}">
-  <dimension ref="A1:V95"/>
+  <dimension ref="A1:V94"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="12.77734375" bestFit="1" customWidth="1"/>
@@ -2550,126 +2541,126 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="12"/>
+      <c r="F1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2" t="s">
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="S1" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="V1" s="5" t="s">
-        <v>396</v>
+      <c r="V1" s="13" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="7" t="s">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4" t="s">
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="Q2" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="2"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="5"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+      <c r="V2" s="13"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3" t="s">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="3" t="s">
+      <c r="F3" s="12"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="2"/>
-      <c r="U3" s="2"/>
-      <c r="V3" s="5"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="11"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
+      <c r="V3" s="13"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -2690,29 +2681,29 @@
       <c r="F4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>29</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>20</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>20</v>
@@ -2730,7 +2721,7 @@
       <c r="T4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="U4" s="11">
+      <c r="U4" s="4">
         <v>3176610428</v>
       </c>
       <c r="V4" s="1">
@@ -2772,7 +2763,7 @@
         <v>34</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>84</v>
@@ -2796,7 +2787,7 @@
       <c r="T5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U5" s="11">
+      <c r="U5" s="4">
         <v>3157772560</v>
       </c>
       <c r="V5" s="1">
@@ -2835,16 +2826,16 @@
         <v>29</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>84</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>20</v>
@@ -2862,7 +2853,7 @@
       <c r="T6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U6" s="11">
+      <c r="U6" s="4">
         <v>3160957716</v>
       </c>
       <c r="V6" s="1">
@@ -2928,7 +2919,7 @@
       <c r="T7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U7" s="11" t="s">
+      <c r="U7" s="4" t="s">
         <v>47</v>
       </c>
       <c r="V7" s="1">
@@ -2967,7 +2958,7 @@
         <v>61</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>42</v>
@@ -2976,7 +2967,7 @@
         <v>83</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>20</v>
@@ -2994,7 +2985,7 @@
       <c r="T8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U8" s="11" t="s">
+      <c r="U8" s="4" t="s">
         <v>54</v>
       </c>
       <c r="V8" s="1">
@@ -3060,7 +3051,7 @@
       <c r="T9" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="U9" s="11">
+      <c r="U9" s="4">
         <v>3176397862</v>
       </c>
       <c r="V9" s="1">
@@ -3126,7 +3117,7 @@
       <c r="T10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U10" s="11">
+      <c r="U10" s="4">
         <v>3144904412</v>
       </c>
       <c r="V10" s="1">
@@ -3141,7 +3132,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>20</v>
@@ -3156,19 +3147,19 @@
         <v>20</v>
       </c>
       <c r="H11" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="J11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="L11" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>84</v>
@@ -3183,16 +3174,16 @@
         <v>29</v>
       </c>
       <c r="Q11" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="R11" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="S11" s="1"/>
       <c r="T11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U11" s="11">
+      <c r="U11" s="4">
         <v>3104909850</v>
       </c>
       <c r="V11" s="1">
@@ -3207,7 +3198,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>20</v>
@@ -3225,7 +3216,7 @@
         <v>32</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>29</v>
@@ -3234,7 +3225,7 @@
         <v>63</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>84</v>
@@ -3249,16 +3240,16 @@
         <v>29</v>
       </c>
       <c r="Q12" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="R12" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="R12" s="1" t="s">
-        <v>166</v>
       </c>
       <c r="S12" s="1"/>
       <c r="T12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U12" s="11">
+      <c r="U12" s="4">
         <v>3234824706</v>
       </c>
       <c r="V12" s="1">
@@ -3273,7 +3264,7 @@
         <v>41</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>20</v>
@@ -3285,10 +3276,10 @@
         <v>46</v>
       </c>
       <c r="G13" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>20</v>
@@ -3297,7 +3288,7 @@
         <v>43</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>42</v>
@@ -3325,7 +3316,7 @@
         <v>20</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="V13" s="1">
         <v>1</v>
@@ -3339,7 +3330,7 @@
         <v>41</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>20</v>
@@ -3384,13 +3375,13 @@
         <v>20</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="S14" s="1"/>
       <c r="T14" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="U14" s="12">
+        <v>172</v>
+      </c>
+      <c r="U14" s="5">
         <v>3022853805</v>
       </c>
       <c r="V14" s="1">
@@ -3405,7 +3396,7 @@
         <v>8</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D15" s="1">
         <v>4</v>
@@ -3420,7 +3411,7 @@
         <v>20</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>20</v>
@@ -3429,34 +3420,34 @@
         <v>61</v>
       </c>
       <c r="K15" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R15" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>178</v>
       </c>
       <c r="S15" s="1"/>
       <c r="T15" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="U15" s="11">
+        <v>178</v>
+      </c>
+      <c r="U15" s="4">
         <v>3145931759</v>
       </c>
       <c r="V15" s="1">
@@ -3471,7 +3462,7 @@
         <v>8</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>20</v>
@@ -3486,7 +3477,7 @@
         <v>20</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>33</v>
@@ -3498,13 +3489,13 @@
         <v>63</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O16" s="1" t="s">
         <v>20</v>
@@ -3513,17 +3504,17 @@
         <v>29</v>
       </c>
       <c r="Q16" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="R16" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="R16" s="1" t="s">
-        <v>184</v>
       </c>
       <c r="S16" s="1"/>
       <c r="T16" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="U16" s="11" t="s">
-        <v>397</v>
+        <v>181</v>
+      </c>
+      <c r="U16" s="4" t="s">
+        <v>396</v>
       </c>
       <c r="V16" s="1">
         <v>1</v>
@@ -3537,7 +3528,7 @@
         <v>41</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>20</v>
@@ -3549,10 +3540,10 @@
         <v>19</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>20</v>
@@ -3576,19 +3567,19 @@
         <v>20</v>
       </c>
       <c r="P17" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R17" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="Q17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R17" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="S17" s="1"/>
       <c r="T17" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U17" s="11">
+      <c r="U17" s="4">
         <v>3186190561</v>
       </c>
       <c r="V17" s="1">
@@ -3603,7 +3594,7 @@
         <v>41</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>20</v>
@@ -3618,7 +3609,7 @@
         <v>20</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>20</v>
@@ -3648,13 +3639,13 @@
         <v>20</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="S18" s="1"/>
       <c r="T18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U18" s="11">
+      <c r="U18" s="4">
         <v>3104502480</v>
       </c>
       <c r="V18" s="1">
@@ -3669,7 +3660,7 @@
         <v>8</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>20</v>
@@ -3684,10 +3675,10 @@
         <v>20</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>29</v>
@@ -3699,7 +3690,7 @@
         <v>42</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>67</v>
@@ -3711,16 +3702,16 @@
         <v>29</v>
       </c>
       <c r="Q19" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="R19" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="R19" s="1" t="s">
-        <v>197</v>
       </c>
       <c r="S19" s="1"/>
       <c r="T19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U19" s="11">
+      <c r="U19" s="4">
         <v>3188584942</v>
       </c>
       <c r="V19" s="1">
@@ -3735,7 +3726,7 @@
         <v>41</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>20</v>
@@ -3747,46 +3738,46 @@
         <v>46</v>
       </c>
       <c r="G20" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="I20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R20" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R20" s="1" t="s">
-        <v>201</v>
       </c>
       <c r="S20" s="1"/>
       <c r="T20" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U20" s="11">
+      <c r="U20" s="4">
         <v>3108490464</v>
       </c>
       <c r="V20" s="1">
@@ -3801,7 +3792,7 @@
         <v>8</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D21" s="1">
         <v>3</v>
@@ -3828,13 +3819,13 @@
         <v>63</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>84</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>20</v>
@@ -3843,17 +3834,17 @@
         <v>29</v>
       </c>
       <c r="Q21" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="R21" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="S21" s="1"/>
       <c r="T21" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="U21" s="11" t="s">
-        <v>398</v>
+        <v>203</v>
+      </c>
+      <c r="U21" s="4" t="s">
+        <v>397</v>
       </c>
       <c r="V21" s="1">
         <v>1</v>
@@ -3867,7 +3858,7 @@
         <v>8</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D22" s="1">
         <v>15</v>
@@ -3882,10 +3873,10 @@
         <v>20</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>29</v>
@@ -3897,28 +3888,28 @@
         <v>42</v>
       </c>
       <c r="M22" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="R22" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>210</v>
       </c>
       <c r="S22" s="1"/>
       <c r="T22" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="U22" s="11">
+        <v>210</v>
+      </c>
+      <c r="U22" s="4">
         <v>3148603281</v>
       </c>
       <c r="V22" s="1">
@@ -3930,10 +3921,10 @@
         <v>98</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>214</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>20</v>
@@ -3945,10 +3936,10 @@
         <v>46</v>
       </c>
       <c r="G23" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>217</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>33</v>
@@ -3960,7 +3951,7 @@
         <v>30</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>20</v>
@@ -3978,14 +3969,14 @@
         <v>20</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="S23" s="1"/>
       <c r="T23" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="U23" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="U23" s="1" t="s">
-        <v>220</v>
       </c>
       <c r="V23" s="1">
         <v>1</v>
@@ -3999,7 +3990,7 @@
         <v>41</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>20</v>
@@ -4014,7 +4005,7 @@
         <v>20</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>33</v>
@@ -4041,16 +4032,16 @@
         <v>51</v>
       </c>
       <c r="Q24" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="R24" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="R24" s="1" t="s">
-        <v>223</v>
       </c>
       <c r="S24" s="1"/>
       <c r="T24" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="U24" s="11">
+        <v>223</v>
+      </c>
+      <c r="U24" s="4">
         <v>3013492810</v>
       </c>
       <c r="V24" s="1">
@@ -4065,7 +4056,7 @@
         <v>8</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>20</v>
@@ -4089,10 +4080,10 @@
         <v>61</v>
       </c>
       <c r="K25" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="L25" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>227</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>84</v>
@@ -4110,14 +4101,14 @@
         <v>20</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="S25" s="1"/>
       <c r="T25" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U25" s="11" t="s">
-        <v>399</v>
+      <c r="U25" s="4" t="s">
+        <v>398</v>
       </c>
       <c r="V25" s="1">
         <v>1</v>
@@ -4131,7 +4122,7 @@
         <v>8</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
@@ -4146,16 +4137,16 @@
         <v>20</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>33</v>
       </c>
       <c r="J26" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="K26" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>231</v>
       </c>
       <c r="L26" s="1" t="s">
         <v>30</v>
@@ -4176,14 +4167,14 @@
         <v>20</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="S26" s="1"/>
       <c r="T26" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U26" s="11" t="s">
-        <v>399</v>
+      <c r="U26" s="4" t="s">
+        <v>398</v>
       </c>
       <c r="V26" s="1">
         <v>1</v>
@@ -4197,34 +4188,34 @@
         <v>8</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="1" t="s">
+      <c r="I27" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="J27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K27" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="J27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="L27" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>20</v>
@@ -4239,17 +4230,17 @@
         <v>29</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="S27" s="1"/>
       <c r="T27" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U27" s="11" t="s">
-        <v>399</v>
+      <c r="U27" s="4" t="s">
+        <v>398</v>
       </c>
       <c r="V27" s="1">
         <v>1</v>
@@ -4263,7 +4254,7 @@
         <v>8</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D28" s="1">
         <v>9</v>
@@ -4275,7 +4266,7 @@
         <v>20</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>84</v>
@@ -4287,10 +4278,10 @@
         <v>61</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>84</v>
@@ -4302,20 +4293,20 @@
         <v>20</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q28" s="1" t="s">
         <v>20</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="S28" s="1"/>
       <c r="T28" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="U28" s="11" t="s">
-        <v>399</v>
+        <v>242</v>
+      </c>
+      <c r="U28" s="4" t="s">
+        <v>398</v>
       </c>
       <c r="V28" s="1">
         <v>1</v>
@@ -4329,7 +4320,7 @@
         <v>8</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>20</v>
@@ -4344,25 +4335,25 @@
         <v>20</v>
       </c>
       <c r="H29" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="I29" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="I29" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="J29" s="1" t="s">
         <v>29</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>84</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O29" s="1" t="s">
         <v>20</v>
@@ -4374,13 +4365,13 @@
         <v>20</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="S29" s="1"/>
       <c r="T29" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="U29" s="11">
+        <v>250</v>
+      </c>
+      <c r="U29" s="4">
         <v>3166221051</v>
       </c>
       <c r="V29" s="1">
@@ -4395,7 +4386,7 @@
         <v>8</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>20</v>
@@ -4419,10 +4410,10 @@
         <v>29</v>
       </c>
       <c r="K30" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L30" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>253</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>67</v>
@@ -4437,16 +4428,16 @@
         <v>29</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="S30" s="1"/>
       <c r="T30" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U30" s="11">
+      <c r="U30" s="4">
         <v>3165559895</v>
       </c>
       <c r="V30" s="1">
@@ -4461,7 +4452,7 @@
         <v>8</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>20</v>
@@ -4476,25 +4467,25 @@
         <v>20</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>29</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>84</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O31" s="1" t="s">
         <v>20</v>
@@ -4503,16 +4494,16 @@
         <v>29</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="S31" s="1"/>
       <c r="T31" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U31" s="11">
+      <c r="U31" s="4">
         <v>3122252784</v>
       </c>
       <c r="V31" s="1">
@@ -4527,7 +4518,7 @@
         <v>41</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>20</v>
@@ -4539,10 +4530,10 @@
         <v>19</v>
       </c>
       <c r="G32" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>263</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>20</v>
@@ -4566,20 +4557,20 @@
         <v>20</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q32" s="1" t="s">
         <v>20</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="S32" s="1"/>
       <c r="T32" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U32" s="11" t="s">
-        <v>400</v>
+      <c r="U32" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="V32" s="1">
         <v>1</v>
@@ -4593,7 +4584,7 @@
         <v>8</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>20</v>
@@ -4608,25 +4599,25 @@
         <v>20</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>29</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>84</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O33" s="1" t="s">
         <v>20</v>
@@ -4638,13 +4629,13 @@
         <v>20</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="S33" s="1"/>
       <c r="T33" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U33" s="11">
+      <c r="U33" s="4">
         <v>3164670196</v>
       </c>
       <c r="V33" s="1">
@@ -4659,7 +4650,7 @@
         <v>8</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>20</v>
@@ -4692,7 +4683,7 @@
         <v>67</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O34" s="1" t="s">
         <v>20</v>
@@ -4704,13 +4695,13 @@
         <v>20</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="S34" s="1"/>
       <c r="T34" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U34" s="11">
+      <c r="U34" s="4">
         <v>3234193130</v>
       </c>
       <c r="V34" s="1">
@@ -4725,7 +4716,7 @@
         <v>8</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>20</v>
@@ -4740,16 +4731,16 @@
         <v>20</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L35" s="1" t="s">
         <v>42</v>
@@ -4770,13 +4761,13 @@
         <v>20</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="S35" s="1"/>
       <c r="T35" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U35" s="11">
+      <c r="U35" s="4">
         <v>3187777421</v>
       </c>
       <c r="V35" s="1">
@@ -4784,7 +4775,7 @@
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="16" t="s">
         <v>111</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -4815,7 +4806,7 @@
         <v>29</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L36" s="1" t="s">
         <v>30</v>
@@ -4833,17 +4824,17 @@
         <v>62</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="S36" s="1"/>
       <c r="T36" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U36" s="11" t="s">
-        <v>401</v>
+      <c r="U36" s="4" t="s">
+        <v>400</v>
       </c>
       <c r="V36" s="1">
         <v>1</v>
@@ -4872,10 +4863,10 @@
         <v>20</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J37" s="1" t="s">
         <v>29</v>
@@ -4902,13 +4893,13 @@
         <v>20</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="S37" s="1"/>
       <c r="T37" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U37" s="11">
+      <c r="U37" s="4">
         <v>3155148175</v>
       </c>
       <c r="V37" s="1">
@@ -4923,7 +4914,7 @@
         <v>41</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>20</v>
@@ -4935,10 +4926,10 @@
         <v>46</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>20</v>
@@ -4953,7 +4944,7 @@
         <v>30</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="N38" s="1" t="s">
         <v>30</v>
@@ -4962,19 +4953,19 @@
         <v>20</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q38" s="1" t="s">
         <v>20</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="S38" s="1"/>
       <c r="T38" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="U38" s="11">
+        <v>280</v>
+      </c>
+      <c r="U38" s="4">
         <v>3168369142</v>
       </c>
       <c r="V38" s="1">
@@ -4989,7 +4980,7 @@
         <v>8</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>20</v>
@@ -5004,7 +4995,7 @@
         <v>20</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>33</v>
@@ -5016,7 +5007,7 @@
         <v>63</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>84</v>
@@ -5034,13 +5025,13 @@
         <v>20</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="S39" s="1"/>
       <c r="T39" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U39" s="11">
+      <c r="U39" s="4">
         <v>3001776812</v>
       </c>
       <c r="V39" s="1">
@@ -5055,7 +5046,7 @@
         <v>8</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>20</v>
@@ -5073,13 +5064,13 @@
         <v>44</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J40" s="1" t="s">
         <v>29</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L40" s="1" t="s">
         <v>42</v>
@@ -5100,14 +5091,14 @@
         <v>20</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="S40" s="1"/>
       <c r="T40" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U40" s="11" t="s">
-        <v>402</v>
+      <c r="U40" s="4" t="s">
+        <v>401</v>
       </c>
       <c r="V40" s="1">
         <v>1</v>
@@ -5121,7 +5112,7 @@
         <v>41</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>20</v>
@@ -5133,10 +5124,10 @@
         <v>46</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>20</v>
@@ -5145,7 +5136,7 @@
         <v>29</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L41" s="1" t="s">
         <v>42</v>
@@ -5163,16 +5154,16 @@
         <v>29</v>
       </c>
       <c r="Q41" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="R41" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="R41" s="1" t="s">
-        <v>290</v>
       </c>
       <c r="S41" s="1"/>
       <c r="T41" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U41" s="11">
+      <c r="U41" s="4">
         <v>3135693608</v>
       </c>
       <c r="V41" s="1">
@@ -5187,7 +5178,7 @@
         <v>41</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>20</v>
@@ -5229,7 +5220,7 @@
         <v>51</v>
       </c>
       <c r="Q42" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="R42" s="1" t="s">
         <v>20</v>
@@ -5238,7 +5229,7 @@
       <c r="T42" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U42" s="11">
+      <c r="U42" s="4">
         <v>3234306552</v>
       </c>
       <c r="V42" s="1">
@@ -5253,7 +5244,7 @@
         <v>41</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>20</v>
@@ -5268,7 +5259,7 @@
         <v>20</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>33</v>
@@ -5283,10 +5274,10 @@
         <v>30</v>
       </c>
       <c r="M43" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="N43" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>296</v>
       </c>
       <c r="O43" s="1" t="s">
         <v>20</v>
@@ -5298,13 +5289,13 @@
         <v>20</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="S43" s="1"/>
       <c r="T43" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U43" s="11">
+      <c r="U43" s="4">
         <v>3127263161</v>
       </c>
       <c r="V43" s="1">
@@ -5319,7 +5310,7 @@
         <v>41</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>20</v>
@@ -5334,7 +5325,7 @@
         <v>20</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>20</v>
@@ -5343,7 +5334,7 @@
         <v>43</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L44" s="1" t="s">
         <v>30</v>
@@ -5361,17 +5352,17 @@
         <v>51</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="S44" s="1"/>
       <c r="T44" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="U44" s="4" t="s">
         <v>301</v>
-      </c>
-      <c r="U44" s="11" t="s">
-        <v>302</v>
       </c>
       <c r="V44" s="1">
         <v>1</v>
@@ -5385,7 +5376,7 @@
         <v>41</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>20</v>
@@ -5400,7 +5391,7 @@
         <v>20</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>20</v>
@@ -5415,10 +5406,10 @@
         <v>42</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O45" s="1" t="s">
         <v>20</v>
@@ -5430,13 +5421,13 @@
         <v>20</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="S45" s="1"/>
       <c r="T45" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U45" s="11">
+      <c r="U45" s="4">
         <v>3225200903</v>
       </c>
       <c r="V45" s="1">
@@ -5451,7 +5442,7 @@
         <v>41</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>20</v>
@@ -5466,7 +5457,7 @@
         <v>20</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>20</v>
@@ -5481,10 +5472,10 @@
         <v>42</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O46" s="1" t="s">
         <v>20</v>
@@ -5496,13 +5487,13 @@
         <v>20</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="S46" s="1"/>
       <c r="T46" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U46" s="11">
+      <c r="U46" s="4">
         <v>32252009003</v>
       </c>
       <c r="V46" s="1">
@@ -5517,7 +5508,7 @@
         <v>8</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>20</v>
@@ -5532,7 +5523,7 @@
         <v>20</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>33</v>
@@ -5559,7 +5550,7 @@
         <v>29</v>
       </c>
       <c r="Q47" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="R47" s="1" t="s">
         <v>20</v>
@@ -5568,7 +5559,7 @@
       <c r="T47" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U47" s="11">
+      <c r="U47" s="4">
         <v>3145154360</v>
       </c>
       <c r="V47" s="1">
@@ -5583,7 +5574,7 @@
         <v>41</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>20</v>
@@ -5598,7 +5589,7 @@
         <v>20</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>20</v>
@@ -5607,16 +5598,16 @@
         <v>29</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L48" s="1" t="s">
         <v>30</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O48" s="1" t="s">
         <v>20</v>
@@ -5625,16 +5616,16 @@
         <v>62</v>
       </c>
       <c r="Q48" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="R48" s="1" t="s">
         <v>310</v>
-      </c>
-      <c r="R48" s="1" t="s">
-        <v>311</v>
       </c>
       <c r="S48" s="1"/>
       <c r="T48" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U48" s="11">
+      <c r="U48" s="4">
         <v>3145120435</v>
       </c>
       <c r="V48" s="1">
@@ -5649,7 +5640,7 @@
         <v>41</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
@@ -5664,7 +5655,7 @@
         <v>20</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>33</v>
@@ -5673,7 +5664,7 @@
         <v>29</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L49" s="1" t="s">
         <v>30</v>
@@ -5691,16 +5682,16 @@
         <v>62</v>
       </c>
       <c r="Q49" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="R49" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="R49" s="1" t="s">
-        <v>316</v>
       </c>
       <c r="S49" s="1"/>
       <c r="T49" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U49" s="11">
+      <c r="U49" s="4">
         <v>3218069056</v>
       </c>
       <c r="V49" s="1">
@@ -5715,7 +5706,7 @@
         <v>41</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>20</v>
@@ -5730,7 +5721,7 @@
         <v>20</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>33</v>
@@ -5739,7 +5730,7 @@
         <v>43</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L50" s="1" t="s">
         <v>30</v>
@@ -5748,7 +5739,7 @@
         <v>20</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O50" s="1" t="s">
         <v>20</v>
@@ -5757,16 +5748,16 @@
         <v>62</v>
       </c>
       <c r="Q50" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="R50" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="R50" s="1" t="s">
-        <v>319</v>
       </c>
       <c r="S50" s="1"/>
       <c r="T50" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U50" s="11">
+      <c r="U50" s="4">
         <v>3207811215</v>
       </c>
       <c r="V50" s="1">
@@ -5781,7 +5772,7 @@
         <v>8</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>20</v>
@@ -5796,25 +5787,25 @@
         <v>20</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J51" s="1" t="s">
         <v>29</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L51" s="1" t="s">
         <v>42</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O51" s="1" t="s">
         <v>20</v>
@@ -5826,14 +5817,14 @@
         <v>20</v>
       </c>
       <c r="R51" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="S51" s="1"/>
       <c r="T51" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U51" s="11" t="s">
-        <v>322</v>
+      <c r="U51" s="4" t="s">
+        <v>321</v>
       </c>
       <c r="V51" s="1">
         <v>1</v>
@@ -5847,7 +5838,7 @@
         <v>41</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
@@ -5889,16 +5880,16 @@
         <v>51</v>
       </c>
       <c r="Q52" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="R52" s="1" t="s">
         <v>80</v>
       </c>
       <c r="S52" s="1"/>
       <c r="T52" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="U52" s="11">
+        <v>322</v>
+      </c>
+      <c r="U52" s="4">
         <v>3052910507</v>
       </c>
       <c r="V52" s="1">
@@ -5913,7 +5904,7 @@
         <v>8</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D53" s="1">
         <v>4</v>
@@ -5940,7 +5931,7 @@
         <v>63</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M53" s="1" t="s">
         <v>84</v>
@@ -5955,16 +5946,16 @@
         <v>29</v>
       </c>
       <c r="Q53" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="R53" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="S53" s="1"/>
       <c r="T53" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="U53" s="11">
+        <v>300</v>
+      </c>
+      <c r="U53" s="4">
         <v>3175359774</v>
       </c>
       <c r="V53" s="1">
@@ -5979,7 +5970,7 @@
         <v>8</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D54" s="1">
         <v>9</v>
@@ -5997,22 +5988,22 @@
         <v>44</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J54" s="1" t="s">
         <v>61</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L54" s="1" t="s">
         <v>42</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O54" s="1" t="s">
         <v>20</v>
@@ -6024,14 +6015,14 @@
         <v>20</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="S54" s="1"/>
       <c r="T54" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="U54" s="11" t="s">
-        <v>403</v>
+        <v>280</v>
+      </c>
+      <c r="U54" s="4" t="s">
+        <v>402</v>
       </c>
       <c r="V54" s="1">
         <v>1</v>
@@ -6045,7 +6036,7 @@
         <v>41</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>20</v>
@@ -6090,13 +6081,13 @@
         <v>20</v>
       </c>
       <c r="R55" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="S55" s="1"/>
       <c r="T55" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="U55" s="11">
+        <v>331</v>
+      </c>
+      <c r="U55" s="4">
         <v>3137532014</v>
       </c>
       <c r="V55" s="1">
@@ -6111,7 +6102,7 @@
         <v>8</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D56" s="1">
         <v>3</v>
@@ -6126,10 +6117,10 @@
         <v>20</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J56" s="1" t="s">
         <v>29</v>
@@ -6138,7 +6129,7 @@
         <v>63</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M56" s="1" t="s">
         <v>67</v>
@@ -6153,16 +6144,16 @@
         <v>29</v>
       </c>
       <c r="Q56" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="R56" s="1" t="s">
         <v>335</v>
-      </c>
-      <c r="R56" s="1" t="s">
-        <v>336</v>
       </c>
       <c r="S56" s="1"/>
       <c r="T56" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="U56" s="11">
+        <v>336</v>
+      </c>
+      <c r="U56" s="4">
         <v>3176474157</v>
       </c>
       <c r="V56" s="1">
@@ -6177,7 +6168,7 @@
         <v>8</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>20</v>
@@ -6207,7 +6198,7 @@
         <v>30</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="N57" s="1" t="s">
         <v>30</v>
@@ -6219,16 +6210,16 @@
         <v>29</v>
       </c>
       <c r="Q57" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="R57" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="R57" s="1" t="s">
-        <v>341</v>
       </c>
       <c r="S57" s="1"/>
       <c r="T57" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U57" s="11">
+      <c r="U57" s="4">
         <v>3206388157</v>
       </c>
       <c r="V57" s="1">
@@ -6243,7 +6234,7 @@
         <v>8</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>20</v>
@@ -6258,7 +6249,7 @@
         <v>20</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>60</v>
@@ -6270,7 +6261,7 @@
         <v>63</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M58" s="1" t="s">
         <v>84</v>
@@ -6285,17 +6276,17 @@
         <v>29</v>
       </c>
       <c r="Q58" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="R58" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="S58" s="1"/>
       <c r="T58" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="U58" s="4" t="s">
         <v>345</v>
-      </c>
-      <c r="U58" s="11" t="s">
-        <v>346</v>
       </c>
       <c r="V58" s="1">
         <v>1</v>
@@ -6309,7 +6300,7 @@
         <v>41</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>20</v>
@@ -6324,7 +6315,7 @@
         <v>20</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>33</v>
@@ -6333,7 +6324,7 @@
         <v>43</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L59" s="1" t="s">
         <v>30</v>
@@ -6348,19 +6339,19 @@
         <v>20</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q59" s="1" t="s">
         <v>20</v>
       </c>
       <c r="R59" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="S59" s="1"/>
       <c r="T59" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U59" s="11">
+      <c r="U59" s="4">
         <v>3505730873</v>
       </c>
       <c r="V59" s="1">
@@ -6375,7 +6366,7 @@
         <v>8</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>20</v>
@@ -6399,35 +6390,35 @@
         <v>43</v>
       </c>
       <c r="K60" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P60" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q60" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R60" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="L60" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M60" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N60" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="O60" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P60" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q60" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R60" s="1" t="s">
-        <v>353</v>
       </c>
       <c r="S60" s="1"/>
       <c r="T60" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U60" s="11" t="s">
-        <v>354</v>
+      <c r="U60" s="4" t="s">
+        <v>353</v>
       </c>
       <c r="V60" s="1">
         <v>1</v>
@@ -6441,7 +6432,7 @@
         <v>8</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>20</v>
@@ -6456,7 +6447,7 @@
         <v>20</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>33</v>
@@ -6465,34 +6456,34 @@
         <v>29</v>
       </c>
       <c r="K61" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="L61" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="L61" s="1" t="s">
+      <c r="M61" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="M61" s="1" t="s">
+      <c r="N61" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P61" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q61" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R61" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="N61" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="O61" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P61" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q61" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R61" s="1" t="s">
-        <v>361</v>
       </c>
       <c r="S61" s="1"/>
       <c r="T61" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U61" s="11">
+      <c r="U61" s="4">
         <v>3153139472</v>
       </c>
       <c r="V61" s="1">
@@ -6507,7 +6498,7 @@
         <v>41</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>20</v>
@@ -6522,7 +6513,7 @@
         <v>20</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>33</v>
@@ -6537,7 +6528,7 @@
         <v>30</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="N62" s="1" t="s">
         <v>30</v>
@@ -6549,16 +6540,16 @@
         <v>51</v>
       </c>
       <c r="Q62" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="R62" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="R62" s="1" t="s">
-        <v>364</v>
       </c>
       <c r="S62" s="1"/>
       <c r="T62" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U62" s="11">
+      <c r="U62" s="4">
         <v>3104296494</v>
       </c>
       <c r="V62" s="1">
@@ -6573,7 +6564,7 @@
         <v>8</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>20</v>
@@ -6588,7 +6579,7 @@
         <v>20</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>33</v>
@@ -6597,35 +6588,35 @@
         <v>29</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L63" s="1" t="s">
         <v>30</v>
       </c>
       <c r="M63" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="N63" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P63" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q63" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R63" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="N63" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="O63" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P63" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q63" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R63" s="1" t="s">
-        <v>367</v>
       </c>
       <c r="S63" s="1"/>
       <c r="T63" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U63" s="11" t="s">
-        <v>368</v>
+      <c r="U63" s="4" t="s">
+        <v>367</v>
       </c>
       <c r="V63" s="1">
         <v>1</v>
@@ -6639,7 +6630,7 @@
         <v>41</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>20</v>
@@ -6681,17 +6672,17 @@
         <v>62</v>
       </c>
       <c r="Q64" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="R64" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="R64" s="1" t="s">
-        <v>370</v>
       </c>
       <c r="S64" s="1"/>
       <c r="T64" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U64" s="11" t="s">
-        <v>371</v>
+      <c r="U64" s="4" t="s">
+        <v>370</v>
       </c>
       <c r="V64" s="1">
         <v>1</v>
@@ -6705,7 +6696,7 @@
         <v>8</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>20</v>
@@ -6720,10 +6711,10 @@
         <v>20</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J65" s="1" t="s">
         <v>29</v>
@@ -6732,13 +6723,13 @@
         <v>63</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M65" s="1" t="s">
         <v>84</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O65" s="1" t="s">
         <v>35</v>
@@ -6750,13 +6741,13 @@
         <v>20</v>
       </c>
       <c r="R65" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="S65" s="1"/>
       <c r="T65" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="U65" s="11">
+        <v>373</v>
+      </c>
+      <c r="U65" s="4">
         <v>3153536463</v>
       </c>
       <c r="V65" s="1">
@@ -6771,7 +6762,7 @@
         <v>8</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>20</v>
@@ -6813,7 +6804,7 @@
         <v>29</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="R66" s="1" t="s">
         <v>20</v>
@@ -6822,8 +6813,8 @@
       <c r="T66" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U66" s="11" t="s">
-        <v>377</v>
+      <c r="U66" s="4" t="s">
+        <v>376</v>
       </c>
       <c r="V66" s="1">
         <v>1</v>
@@ -6837,7 +6828,7 @@
         <v>8</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>20</v>
@@ -6852,10 +6843,10 @@
         <v>20</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J67" s="1" t="s">
         <v>29</v>
@@ -6864,31 +6855,31 @@
         <v>63</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M67" s="1" t="s">
         <v>84</v>
       </c>
       <c r="N67" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P67" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q67" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="R67" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="O67" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P67" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q67" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="R67" s="1" t="s">
-        <v>381</v>
       </c>
       <c r="S67" s="1"/>
       <c r="T67" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U67" s="11">
+      <c r="U67" s="4">
         <v>3206886224</v>
       </c>
       <c r="V67" s="1">
@@ -6903,7 +6894,7 @@
         <v>8</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>20</v>
@@ -6918,10 +6909,10 @@
         <v>20</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J68" s="1" t="s">
         <v>29</v>
@@ -6930,13 +6921,13 @@
         <v>63</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O68" s="1" t="s">
         <v>20</v>
@@ -6945,16 +6936,16 @@
         <v>29</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="R68" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="S68" s="1"/>
       <c r="T68" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U68" s="11">
+      <c r="U68" s="4">
         <v>3138414689</v>
       </c>
       <c r="V68" s="1">
@@ -6969,7 +6960,7 @@
         <v>41</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>20</v>
@@ -7011,17 +7002,17 @@
         <v>51</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="R69" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="S69" s="1"/>
       <c r="T69" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U69" s="11" t="s">
-        <v>389</v>
+      <c r="U69" s="4" t="s">
+        <v>388</v>
       </c>
       <c r="V69" s="1">
         <v>1</v>
@@ -7035,7 +7026,7 @@
         <v>41</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D70" s="1">
         <v>4</v>
@@ -7050,7 +7041,7 @@
         <v>20</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>33</v>
@@ -7080,13 +7071,13 @@
         <v>20</v>
       </c>
       <c r="R70" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="S70" s="1"/>
       <c r="T70" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U70" s="11">
+      <c r="U70" s="4">
         <v>3005550667</v>
       </c>
       <c r="V70" s="1">
@@ -7101,7 +7092,7 @@
         <v>41</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>20</v>
@@ -7113,46 +7104,46 @@
         <v>46</v>
       </c>
       <c r="G71" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M71" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N71" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="O71" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P71" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q71" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="R71" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="H71" s="1" t="s">
+      <c r="T71" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="U71" s="6" t="s">
         <v>409</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J71" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="L71" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="M71" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="N71" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="O71" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P71" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q71" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R71" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="T71" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="U71">
-        <v>3170632496</v>
       </c>
       <c r="V71" s="1">
         <v>2</v>
@@ -7163,10 +7154,10 @@
         <v>147</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>20</v>
@@ -7175,13 +7166,13 @@
         <v>20</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>248</v>
+        <v>84</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>20</v>
@@ -7190,40 +7181,40 @@
         <v>29</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>30</v>
+        <v>226</v>
       </c>
       <c r="M72" s="1" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>248</v>
+        <v>84</v>
       </c>
       <c r="O72" s="1" t="s">
         <v>20</v>
       </c>
       <c r="P72" s="1" t="s">
-        <v>242</v>
+        <v>29</v>
       </c>
       <c r="Q72" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="R72" s="6" t="s">
         <v>411</v>
       </c>
-      <c r="R72" s="1" t="s">
-        <v>412</v>
-      </c>
       <c r="T72" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U72" s="13" t="s">
-        <v>413</v>
+      <c r="U72" s="6">
+        <v>3014296553</v>
       </c>
       <c r="V72" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>148</v>
       </c>
@@ -7231,7 +7222,7 @@
         <v>8</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>20</v>
@@ -7240,13 +7231,13 @@
         <v>20</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>20</v>
@@ -7255,16 +7246,16 @@
         <v>29</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>241</v>
+        <v>63</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>227</v>
+        <v>64</v>
       </c>
       <c r="M73" s="1" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="O73" s="1" t="s">
         <v>20</v>
@@ -7273,22 +7264,19 @@
         <v>29</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="R73" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="R73" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="T73" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="U73" s="13">
-        <v>3014296553</v>
+      <c r="U73" s="7" t="s">
+        <v>419</v>
       </c>
       <c r="V73" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>149</v>
       </c>
@@ -7296,7 +7284,7 @@
         <v>8</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>20</v>
@@ -7311,26 +7299,26 @@
         <v>20</v>
       </c>
       <c r="H74" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="M74" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="N74" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="I74" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J74" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="L74" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="M74" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="N74" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="O74" s="1" t="s">
         <v>20</v>
       </c>
@@ -7338,13 +7326,16 @@
         <v>29</v>
       </c>
       <c r="Q74" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R74" s="13" t="s">
-        <v>419</v>
-      </c>
-      <c r="U74" s="14" t="s">
-        <v>423</v>
+        <v>418</v>
+      </c>
+      <c r="R74" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="T74" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="U74" s="6" t="s">
+        <v>420</v>
       </c>
       <c r="V74" s="1">
         <v>2</v>
@@ -7358,7 +7349,7 @@
         <v>8</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>418</v>
+        <v>536</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>20</v>
@@ -7373,25 +7364,25 @@
         <v>20</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>40</v>
+        <v>538</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>156</v>
+        <v>33</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>357</v>
+        <v>29</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>241</v>
+        <v>20</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M75" s="1" t="s">
-        <v>84</v>
+        <v>539</v>
       </c>
       <c r="N75" s="1" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="O75" s="1" t="s">
         <v>20</v>
@@ -7400,19 +7391,19 @@
         <v>29</v>
       </c>
       <c r="Q75" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="R75" s="13" t="s">
-        <v>420</v>
+        <v>540</v>
+      </c>
+      <c r="R75" s="6" t="s">
+        <v>541</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="U75" s="13" t="s">
-        <v>424</v>
+        <v>20</v>
+      </c>
+      <c r="U75" s="6">
+        <v>3145076306</v>
       </c>
       <c r="V75" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.3">
@@ -7423,7 +7414,7 @@
         <v>8</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>20</v>
@@ -7438,22 +7429,22 @@
         <v>20</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>542</v>
+        <v>30</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="J76" s="1" t="s">
         <v>29</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>227</v>
+        <v>30</v>
       </c>
       <c r="M76" s="1" t="s">
-        <v>543</v>
+        <v>30</v>
       </c>
       <c r="N76" s="1" t="s">
         <v>30</v>
@@ -7465,15 +7456,15 @@
         <v>29</v>
       </c>
       <c r="Q76" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="R76" s="13" t="s">
-        <v>545</v>
+        <v>20</v>
+      </c>
+      <c r="R76" s="6" t="s">
+        <v>541</v>
       </c>
       <c r="T76" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U76" s="13">
+      <c r="U76" s="6">
         <v>3145076306</v>
       </c>
       <c r="V76" s="1">
@@ -7482,13 +7473,13 @@
     </row>
     <row r="77" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>152</v>
+        <v>534</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>20</v>
@@ -7497,22 +7488,22 @@
         <v>20</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="L77" s="1" t="s">
         <v>30</v>
@@ -7530,30 +7521,30 @@
         <v>29</v>
       </c>
       <c r="Q77" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R77" s="13" t="s">
+        <v>542</v>
+      </c>
+      <c r="R77" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="T77" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="U77" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="T77" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="U77" s="13">
-        <v>3145076306</v>
-      </c>
       <c r="V77" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>538</v>
+        <v>565</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>539</v>
+        <v>577</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>20</v>
@@ -7562,31 +7553,31 @@
         <v>20</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>32</v>
+        <v>495</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>33</v>
+        <v>342</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>30</v>
+        <v>508</v>
       </c>
       <c r="M78" s="1" t="s">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="O78" s="1" t="s">
         <v>20</v>
@@ -7595,30 +7586,30 @@
         <v>29</v>
       </c>
       <c r="Q78" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="R78" s="13" t="s">
-        <v>547</v>
+        <v>578</v>
+      </c>
+      <c r="R78" s="6" t="s">
+        <v>579</v>
       </c>
       <c r="T78" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="U78" s="1" t="s">
-        <v>549</v>
+        <v>20</v>
+      </c>
+      <c r="U78" t="s">
+        <v>564</v>
       </c>
       <c r="V78" s="1">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="79" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>20</v>
@@ -7633,75 +7624,75 @@
         <v>20</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>499</v>
+        <v>30</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>343</v>
+        <v>20</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>512</v>
+        <v>30</v>
       </c>
       <c r="M79" s="1" t="s">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="O79" s="1" t="s">
         <v>20</v>
       </c>
       <c r="P79" s="1" t="s">
-        <v>29</v>
+        <v>187</v>
       </c>
       <c r="Q79" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="R79" s="13" t="s">
-        <v>583</v>
+        <v>598</v>
+      </c>
+      <c r="R79" s="6" t="s">
+        <v>599</v>
       </c>
       <c r="T79" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U79" t="s">
-        <v>568</v>
+      <c r="U79">
+        <v>3052910507</v>
       </c>
       <c r="V79" s="1">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C80" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G80" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="D80" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="H80" s="1" t="s">
-        <v>30</v>
+        <v>308</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="J80" s="1" t="s">
         <v>43</v>
@@ -7722,19 +7713,19 @@
         <v>20</v>
       </c>
       <c r="P80" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q80" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R80" s="6" t="s">
         <v>602</v>
       </c>
-      <c r="R80" s="13" t="s">
-        <v>603</v>
-      </c>
       <c r="T80" s="1" t="s">
         <v>20</v>
       </c>
       <c r="U80">
-        <v>3052910507</v>
+        <v>3218227206</v>
       </c>
       <c r="V80" s="1">
         <v>10</v>
@@ -7742,78 +7733,78 @@
     </row>
     <row r="81" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C81" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L81" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M81" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="N81" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="O81" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P81" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q81" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="R81" s="6" t="s">
         <v>604</v>
       </c>
-      <c r="D81" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G81" s="1" t="s">
+      <c r="T81" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="H81" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J81" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K81" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L81" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M81" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N81" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="O81" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P81" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q81" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R81" s="13" t="s">
+      <c r="U81" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="T81" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="U81">
-        <v>3218227206</v>
-      </c>
       <c r="V81" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>20</v>
@@ -7825,10 +7816,10 @@
         <v>46</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>187</v>
+        <v>20</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>20</v>
@@ -7843,42 +7834,42 @@
         <v>30</v>
       </c>
       <c r="M82" s="1" t="s">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O82" s="1" t="s">
         <v>20</v>
       </c>
       <c r="P82" s="1" t="s">
-        <v>29</v>
+        <v>241</v>
       </c>
       <c r="Q82" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="R82" s="13" t="s">
-        <v>608</v>
+        <v>613</v>
+      </c>
+      <c r="R82" s="6" t="s">
+        <v>614</v>
       </c>
       <c r="T82" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="U82" s="1" t="s">
-        <v>610</v>
+        <v>615</v>
+      </c>
+      <c r="U82">
+        <v>3183590155</v>
       </c>
       <c r="V82" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>20</v>
@@ -7887,49 +7878,49 @@
         <v>20</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>20</v>
+        <v>235</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>42</v>
+        <v>240</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>30</v>
+        <v>226</v>
       </c>
       <c r="M83" s="1" t="s">
-        <v>295</v>
+        <v>84</v>
       </c>
       <c r="N83" s="1" t="s">
-        <v>309</v>
+        <v>84</v>
       </c>
       <c r="O83" s="1" t="s">
         <v>20</v>
       </c>
       <c r="P83" s="1" t="s">
-        <v>242</v>
+        <v>29</v>
       </c>
       <c r="Q83" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="R83" s="13" t="s">
         <v>618</v>
       </c>
+      <c r="R83" s="6" t="s">
+        <v>619</v>
+      </c>
       <c r="T83" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="U83">
-        <v>3183590155</v>
+        <v>20</v>
+      </c>
+      <c r="U83" s="1" t="s">
+        <v>620</v>
       </c>
       <c r="V83" s="1">
         <v>16</v>
@@ -7937,13 +7928,13 @@
     </row>
     <row r="84" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>20</v>
@@ -7958,25 +7949,25 @@
         <v>20</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>621</v>
+        <v>32</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>236</v>
+        <v>33</v>
       </c>
       <c r="J84" s="1" t="s">
         <v>29</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>241</v>
+        <v>63</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>227</v>
+        <v>30</v>
       </c>
       <c r="M84" s="1" t="s">
         <v>84</v>
       </c>
       <c r="N84" s="1" t="s">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="O84" s="1" t="s">
         <v>20</v>
@@ -7987,14 +7978,11 @@
       <c r="Q84" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="R84" s="13" t="s">
+      <c r="R84" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="T84" s="1" t="s">
         <v>623</v>
-      </c>
-      <c r="T84" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="U84" s="1" t="s">
-        <v>624</v>
       </c>
       <c r="V84" s="1">
         <v>16</v>
@@ -8002,13 +7990,13 @@
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>20</v>
@@ -8023,7 +8011,7 @@
         <v>20</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>32</v>
+        <v>625</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>33</v>
@@ -8035,13 +8023,13 @@
         <v>63</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>30</v>
+        <v>226</v>
       </c>
       <c r="M85" s="1" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="O85" s="1" t="s">
         <v>20</v>
@@ -8050,13 +8038,16 @@
         <v>29</v>
       </c>
       <c r="Q85" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R85" s="6" t="s">
         <v>626</v>
       </c>
-      <c r="R85" s="13" t="s">
-        <v>631</v>
-      </c>
       <c r="T85" s="1" t="s">
-        <v>627</v>
+        <v>20</v>
+      </c>
+      <c r="U85" s="1" t="s">
+        <v>628</v>
       </c>
       <c r="V85" s="1">
         <v>16</v>
@@ -8064,13 +8055,13 @@
     </row>
     <row r="86" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>20</v>
@@ -8079,13 +8070,13 @@
         <v>20</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>629</v>
+        <v>539</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>33</v>
@@ -8094,16 +8085,16 @@
         <v>29</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>63</v>
+        <v>176</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M86" s="1" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>67</v>
+        <v>365</v>
       </c>
       <c r="O86" s="1" t="s">
         <v>20</v>
@@ -8114,14 +8105,14 @@
       <c r="Q86" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="R86" s="13" t="s">
+      <c r="R86" s="6" t="s">
         <v>630</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="U86" s="1" t="s">
-        <v>632</v>
+        <v>344</v>
+      </c>
+      <c r="U86">
+        <v>3218036176</v>
       </c>
       <c r="V86" s="1">
         <v>16</v>
@@ -8129,13 +8120,13 @@
     </row>
     <row r="87" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>633</v>
+        <v>189</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>20</v>
@@ -8144,49 +8135,49 @@
         <v>20</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>543</v>
+        <v>84</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>177</v>
+        <v>30</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>227</v>
+        <v>631</v>
       </c>
       <c r="M87" s="1" t="s">
         <v>84</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>366</v>
+        <v>84</v>
       </c>
       <c r="O87" s="1" t="s">
         <v>20</v>
       </c>
       <c r="P87" s="1" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="Q87" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="R87" s="13" t="s">
-        <v>634</v>
+      <c r="R87" s="6" t="s">
+        <v>632</v>
       </c>
       <c r="T87" s="1" t="s">
-        <v>345</v>
+        <v>20</v>
       </c>
       <c r="U87">
-        <v>3218036176</v>
+        <v>3104502480</v>
       </c>
       <c r="V87" s="1">
         <v>16</v>
@@ -8194,31 +8185,31 @@
     </row>
     <row r="88" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>20</v>
+        <v>633</v>
+      </c>
+      <c r="D88" s="1">
+        <v>2</v>
+      </c>
+      <c r="E88" s="1">
+        <v>0</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>20</v>
+        <v>634</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>84</v>
+        <v>635</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="J88" s="1" t="s">
         <v>43</v>
@@ -8227,31 +8218,31 @@
         <v>30</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>635</v>
+        <v>30</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="O88" s="1" t="s">
         <v>20</v>
       </c>
       <c r="P88" s="1" t="s">
-        <v>51</v>
+        <v>187</v>
       </c>
       <c r="Q88" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="R88" s="13" t="s">
+      <c r="R88" s="1" t="s">
         <v>636</v>
       </c>
       <c r="T88" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U88">
-        <v>3104502480</v>
+      <c r="U88" s="1" t="s">
+        <v>637</v>
       </c>
       <c r="V88" s="1">
         <v>16</v>
@@ -8259,57 +8250,57 @@
     </row>
     <row r="89" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="D89" s="1">
-        <v>2</v>
-      </c>
-      <c r="E89" s="1">
-        <v>0</v>
+        <v>638</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>638</v>
+        <v>20</v>
       </c>
       <c r="H89" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L89" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="M89" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="N89" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="O89" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P89" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q89" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="I89" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J89" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K89" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L89" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M89" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="N89" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="O89" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P89" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q89" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R89" s="1" t="s">
+      <c r="R89" s="6" t="s">
         <v>640</v>
       </c>
       <c r="T89" s="1" t="s">
@@ -8324,13 +8315,13 @@
     </row>
     <row r="90" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>580</v>
+        <v>642</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>20</v>
@@ -8345,10 +8336,10 @@
         <v>20</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>154</v>
+        <v>32</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>245</v>
+        <v>33</v>
       </c>
       <c r="J90" s="1" t="s">
         <v>29</v>
@@ -8357,13 +8348,13 @@
         <v>63</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>227</v>
+        <v>30</v>
       </c>
       <c r="M90" s="1" t="s">
         <v>84</v>
       </c>
       <c r="N90" s="1" t="s">
-        <v>257</v>
+        <v>30</v>
       </c>
       <c r="O90" s="1" t="s">
         <v>20</v>
@@ -8372,16 +8363,16 @@
         <v>29</v>
       </c>
       <c r="Q90" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="R90" s="13" t="s">
-        <v>644</v>
+        <v>651</v>
+      </c>
+      <c r="R90" s="6" t="s">
+        <v>652</v>
       </c>
       <c r="T90" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U90" s="1" t="s">
-        <v>645</v>
+      <c r="U90">
+        <v>3114711135</v>
       </c>
       <c r="V90" s="1">
         <v>16</v>
@@ -8389,13 +8380,13 @@
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>20</v>
@@ -8410,25 +8401,25 @@
         <v>20</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>32</v>
+        <v>654</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>33</v>
+        <v>155</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>29</v>
+        <v>655</v>
       </c>
       <c r="K91" s="1" t="s">
         <v>63</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>30</v>
+        <v>226</v>
       </c>
       <c r="M91" s="1" t="s">
         <v>84</v>
       </c>
       <c r="N91" s="1" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="O91" s="1" t="s">
         <v>20</v>
@@ -8437,16 +8428,16 @@
         <v>29</v>
       </c>
       <c r="Q91" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="R91" s="13" t="s">
         <v>656</v>
       </c>
+      <c r="R91" s="6" t="s">
+        <v>657</v>
+      </c>
       <c r="T91" s="1" t="s">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="U91">
-        <v>3114711135</v>
+        <v>3002654064</v>
       </c>
       <c r="V91" s="1">
         <v>16</v>
@@ -8454,13 +8445,13 @@
     </row>
     <row r="92" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>20</v>
@@ -8469,28 +8460,28 @@
         <v>20</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>658</v>
+        <v>495</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>156</v>
+        <v>342</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>659</v>
+        <v>29</v>
       </c>
       <c r="K92" s="1" t="s">
         <v>63</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="N92" s="1" t="s">
         <v>67</v>
@@ -8502,16 +8493,16 @@
         <v>29</v>
       </c>
       <c r="Q92" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="R92" s="6" t="s">
         <v>660</v>
       </c>
-      <c r="R92" s="13" t="s">
-        <v>661</v>
-      </c>
       <c r="T92" s="1" t="s">
-        <v>301</v>
+        <v>20</v>
       </c>
       <c r="U92">
-        <v>3002654064</v>
+        <v>3184694842</v>
       </c>
       <c r="V92" s="1">
         <v>16</v>
@@ -8519,13 +8510,13 @@
     </row>
     <row r="93" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>20</v>
@@ -8540,22 +8531,22 @@
         <v>20</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>499</v>
+        <v>512</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>343</v>
+        <v>33</v>
       </c>
       <c r="J93" s="1" t="s">
         <v>29</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>63</v>
+        <v>240</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M93" s="1" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="N93" s="1" t="s">
         <v>67</v>
@@ -8567,16 +8558,16 @@
         <v>29</v>
       </c>
       <c r="Q93" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="R93" s="6" t="s">
         <v>663</v>
       </c>
-      <c r="R93" s="13" t="s">
+      <c r="T93" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="U93" s="1" t="s">
         <v>664</v>
-      </c>
-      <c r="T93" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="U93">
-        <v>3184694842</v>
       </c>
       <c r="V93" s="1">
         <v>16</v>
@@ -8584,96 +8575,31 @@
     </row>
     <row r="94" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>665</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H94" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J94" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K94" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="L94" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="M94" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="N94" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="O94" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P94" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q94" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="R94" s="13" t="s">
-        <v>667</v>
-      </c>
-      <c r="T94" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="U94" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="V94" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A95" s="1" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:E2"/>
+    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="G1:Q1"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="Q2:Q3"/>
     <mergeCell ref="U1:U3"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="S1:S3"/>
     <mergeCell ref="V1:V3"/>
-    <mergeCell ref="F1:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="N2:N3"/>
     <mergeCell ref="O2:O3"/>
-    <mergeCell ref="G1:Q1"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="Q2:Q3"/>
     <mergeCell ref="R1:R3"/>
     <mergeCell ref="T1:T3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:E2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8698,130 +8624,130 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="12"/>
+      <c r="F1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="8" t="s">
-        <v>439</v>
-      </c>
-      <c r="S1" s="2" t="s">
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="S1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="T1" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="V1" s="5" t="s">
-        <v>396</v>
+      <c r="V1" s="13" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="7" t="s">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4" t="s">
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="Q2" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="9"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="5"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="12"/>
+      <c r="V2" s="13"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3" t="s">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="3" t="s">
+      <c r="F3" s="12"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="2"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="2"/>
-      <c r="V3" s="5"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="11"/>
+      <c r="U3" s="12"/>
+      <c r="V3" s="13"/>
     </row>
     <row r="4" spans="1:22" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="B4" t="s">
         <v>41</v>
@@ -8842,7 +8768,7 @@
         <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I4" t="s">
         <v>33</v>
@@ -8869,16 +8795,16 @@
         <v>51</v>
       </c>
       <c r="Q4" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="R4" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="S4" t="s">
-        <v>441</v>
-      </c>
-      <c r="U4" s="15" t="s">
-        <v>442</v>
+        <v>437</v>
+      </c>
+      <c r="U4" s="8" t="s">
+        <v>438</v>
       </c>
       <c r="V4">
         <v>3</v>
@@ -8886,7 +8812,7 @@
     </row>
     <row r="5" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B5" t="s">
         <v>41</v>
@@ -8916,7 +8842,7 @@
         <v>43</v>
       </c>
       <c r="K5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L5" t="s">
         <v>30</v>
@@ -8925,7 +8851,7 @@
         <v>84</v>
       </c>
       <c r="N5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O5" t="s">
         <v>20</v>
@@ -8934,16 +8860,16 @@
         <v>51</v>
       </c>
       <c r="Q5" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="R5" t="s">
         <v>20</v>
       </c>
       <c r="S5" t="s">
-        <v>447</v>
-      </c>
-      <c r="U5" s="14" t="s">
-        <v>448</v>
+        <v>443</v>
+      </c>
+      <c r="U5" s="7" t="s">
+        <v>444</v>
       </c>
       <c r="V5">
         <v>3</v>
@@ -8951,7 +8877,7 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B6" t="s">
         <v>41</v>
@@ -8972,7 +8898,7 @@
         <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I6" t="s">
         <v>33</v>
@@ -8996,16 +8922,16 @@
         <v>20</v>
       </c>
       <c r="P6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q6" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="R6" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="S6" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="U6" t="s">
         <v>20</v>
@@ -9016,7 +8942,7 @@
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="B7" t="s">
         <v>41</v>
@@ -9037,7 +8963,7 @@
         <v>20</v>
       </c>
       <c r="H7" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="I7" t="s">
         <v>33</v>
@@ -9064,13 +8990,13 @@
         <v>62</v>
       </c>
       <c r="Q7" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="R7" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="S7" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="U7" t="s">
         <v>20</v>
@@ -9081,7 +9007,7 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B8" t="s">
         <v>41</v>
@@ -9102,7 +9028,7 @@
         <v>20</v>
       </c>
       <c r="H8" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="I8" t="s">
         <v>20</v>
@@ -9117,10 +9043,10 @@
         <v>30</v>
       </c>
       <c r="M8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="N8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O8" t="s">
         <v>20</v>
@@ -9132,10 +9058,10 @@
         <v>20</v>
       </c>
       <c r="R8" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="S8" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="U8" t="s">
         <v>20</v>
@@ -9146,7 +9072,7 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B9" t="s">
         <v>41</v>
@@ -9167,7 +9093,7 @@
         <v>20</v>
       </c>
       <c r="H9" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="I9" t="s">
         <v>33</v>
@@ -9185,7 +9111,7 @@
         <v>84</v>
       </c>
       <c r="N9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O9" t="s">
         <v>20</v>
@@ -9197,10 +9123,10 @@
         <v>20</v>
       </c>
       <c r="R9" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="S9" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="U9" t="s">
         <v>20</v>
@@ -9211,7 +9137,7 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="B10" t="s">
         <v>41</v>
@@ -9262,10 +9188,10 @@
         <v>20</v>
       </c>
       <c r="R10" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="S10" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="U10" t="s">
         <v>20</v>
@@ -9276,7 +9202,7 @@
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B11" t="s">
         <v>41</v>
@@ -9297,7 +9223,7 @@
         <v>20</v>
       </c>
       <c r="H11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I11" t="s">
         <v>33</v>
@@ -9327,10 +9253,10 @@
         <v>20</v>
       </c>
       <c r="R11" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="S11" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="U11" t="s">
         <v>20</v>
@@ -9341,7 +9267,7 @@
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="B12" t="s">
         <v>41</v>
@@ -9359,10 +9285,10 @@
         <v>20</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H12" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="I12" t="s">
         <v>20</v>
@@ -9386,16 +9312,16 @@
         <v>20</v>
       </c>
       <c r="P12" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="Q12" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="R12" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="S12" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="U12" t="s">
         <v>20</v>
@@ -9406,7 +9332,7 @@
     </row>
     <row r="13" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="B13" t="s">
         <v>41</v>
@@ -9427,7 +9353,7 @@
         <v>20</v>
       </c>
       <c r="H13" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="I13" t="s">
         <v>33</v>
@@ -9454,16 +9380,16 @@
         <v>29</v>
       </c>
       <c r="Q13" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="R13" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="S13" t="s">
-        <v>466</v>
-      </c>
-      <c r="U13" s="14" t="s">
-        <v>467</v>
+        <v>462</v>
+      </c>
+      <c r="U13" s="7" t="s">
+        <v>463</v>
       </c>
       <c r="V13">
         <v>3</v>
@@ -9471,7 +9397,7 @@
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="B14" t="s">
         <v>41</v>
@@ -9492,7 +9418,7 @@
         <v>20</v>
       </c>
       <c r="H14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I14" t="s">
         <v>20</v>
@@ -9507,10 +9433,10 @@
         <v>30</v>
       </c>
       <c r="M14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="N14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O14" t="s">
         <v>20</v>
@@ -9519,13 +9445,13 @@
         <v>62</v>
       </c>
       <c r="Q14" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="R14" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="S14" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="U14" t="s">
         <v>20</v>
@@ -9536,7 +9462,7 @@
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="B15" t="s">
         <v>41</v>
@@ -9557,7 +9483,7 @@
         <v>20</v>
       </c>
       <c r="H15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I15" t="s">
         <v>33</v>
@@ -9566,7 +9492,7 @@
         <v>43</v>
       </c>
       <c r="K15" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L15" t="s">
         <v>30</v>
@@ -9584,13 +9510,13 @@
         <v>51</v>
       </c>
       <c r="Q15" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="R15" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="S15" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="U15" t="s">
         <v>20</v>
@@ -9601,7 +9527,7 @@
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="B16" t="s">
         <v>41</v>
@@ -9622,7 +9548,7 @@
         <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="I16" t="s">
         <v>33</v>
@@ -9631,16 +9557,16 @@
         <v>43</v>
       </c>
       <c r="K16" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="L16" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M16" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="N16" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O16" t="s">
         <v>20</v>
@@ -9649,13 +9575,13 @@
         <v>51</v>
       </c>
       <c r="Q16" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="R16" t="s">
         <v>20</v>
       </c>
       <c r="S16" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="U16" t="s">
         <v>20</v>
@@ -9666,7 +9592,7 @@
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B17" t="s">
         <v>41</v>
@@ -9687,7 +9613,7 @@
         <v>20</v>
       </c>
       <c r="H17" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="I17" t="s">
         <v>33</v>
@@ -9696,16 +9622,16 @@
         <v>43</v>
       </c>
       <c r="K17" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L17" t="s">
         <v>30</v>
       </c>
       <c r="M17" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="N17" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="O17" t="s">
         <v>20</v>
@@ -9714,13 +9640,13 @@
         <v>51</v>
       </c>
       <c r="Q17" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="R17" t="s">
         <v>20</v>
       </c>
       <c r="S17" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="U17" t="s">
         <v>20</v>
@@ -9731,7 +9657,7 @@
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B18" t="s">
         <v>41</v>
@@ -9752,7 +9678,7 @@
         <v>20</v>
       </c>
       <c r="H18" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="I18" t="s">
         <v>33</v>
@@ -9779,13 +9705,13 @@
         <v>51</v>
       </c>
       <c r="Q18" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="R18" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="S18" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="U18" t="s">
         <v>20</v>
@@ -9796,7 +9722,7 @@
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="B19" t="s">
         <v>41</v>
@@ -9817,7 +9743,7 @@
         <v>20</v>
       </c>
       <c r="H19" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="I19" t="s">
         <v>33</v>
@@ -9826,7 +9752,7 @@
         <v>29</v>
       </c>
       <c r="K19" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L19" t="s">
         <v>30</v>
@@ -9835,7 +9761,7 @@
         <v>84</v>
       </c>
       <c r="N19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O19" t="s">
         <v>20</v>
@@ -9844,13 +9770,13 @@
         <v>62</v>
       </c>
       <c r="Q19" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="R19" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="S19" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="U19" t="s">
         <v>20</v>
@@ -9861,7 +9787,7 @@
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
@@ -9882,7 +9808,7 @@
         <v>20</v>
       </c>
       <c r="H20" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="I20" t="s">
         <v>33</v>
@@ -9894,13 +9820,13 @@
         <v>63</v>
       </c>
       <c r="L20" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s">
         <v>84</v>
       </c>
       <c r="N20" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O20" t="s">
         <v>20</v>
@@ -9909,13 +9835,13 @@
         <v>29</v>
       </c>
       <c r="Q20" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="R20" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="S20" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="U20" t="s">
         <v>20</v>
@@ -9926,7 +9852,7 @@
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B21" t="s">
         <v>8</v>
@@ -9947,10 +9873,10 @@
         <v>20</v>
       </c>
       <c r="H21" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="I21" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J21" t="s">
         <v>29</v>
@@ -9959,13 +9885,13 @@
         <v>63</v>
       </c>
       <c r="L21" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M21" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="N21" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="O21" t="s">
         <v>20</v>
@@ -9977,10 +9903,10 @@
         <v>20</v>
       </c>
       <c r="R21" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="S21" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="U21" t="s">
         <v>20</v>
@@ -9991,7 +9917,7 @@
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B22" t="s">
         <v>8</v>
@@ -10012,10 +9938,10 @@
         <v>20</v>
       </c>
       <c r="H22" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="I22" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J22" t="s">
         <v>29</v>
@@ -10024,13 +9950,13 @@
         <v>63</v>
       </c>
       <c r="L22" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M22" t="s">
         <v>84</v>
       </c>
       <c r="N22" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="O22" t="s">
         <v>20</v>
@@ -10042,10 +9968,10 @@
         <v>20</v>
       </c>
       <c r="R22" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="S22" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="U22" t="s">
         <v>20</v>
@@ -10056,7 +9982,7 @@
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B23" t="s">
         <v>8</v>
@@ -10077,10 +10003,10 @@
         <v>20</v>
       </c>
       <c r="H23" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="I23" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J23" t="s">
         <v>29</v>
@@ -10089,13 +10015,13 @@
         <v>20</v>
       </c>
       <c r="L23" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M23" t="s">
         <v>84</v>
       </c>
       <c r="N23" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O23" t="s">
         <v>20</v>
@@ -10104,13 +10030,13 @@
         <v>29</v>
       </c>
       <c r="Q23" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="R23" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="S23" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="U23" t="s">
         <v>20</v>
@@ -10121,7 +10047,7 @@
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B24" t="s">
         <v>8</v>
@@ -10142,7 +10068,7 @@
         <v>20</v>
       </c>
       <c r="H24" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="I24" t="s">
         <v>33</v>
@@ -10154,13 +10080,13 @@
         <v>63</v>
       </c>
       <c r="L24" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M24" t="s">
         <v>84</v>
       </c>
       <c r="N24" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="O24" t="s">
         <v>20</v>
@@ -10169,13 +10095,13 @@
         <v>29</v>
       </c>
       <c r="Q24" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="R24" t="s">
         <v>20</v>
       </c>
       <c r="S24" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="U24" t="s">
         <v>20</v>
@@ -10186,7 +10112,7 @@
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="B25" t="s">
         <v>8</v>
@@ -10207,10 +10133,10 @@
         <v>20</v>
       </c>
       <c r="H25" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="I25" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J25" t="s">
         <v>29</v>
@@ -10219,7 +10145,7 @@
         <v>63</v>
       </c>
       <c r="L25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M25" t="s">
         <v>20</v>
@@ -10234,13 +10160,13 @@
         <v>29</v>
       </c>
       <c r="Q25" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="R25" t="s">
         <v>20</v>
       </c>
       <c r="S25" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="U25" t="s">
         <v>20</v>
@@ -10251,7 +10177,7 @@
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="B26" t="s">
         <v>8</v>
@@ -10284,7 +10210,7 @@
         <v>20</v>
       </c>
       <c r="L26" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M26" t="s">
         <v>20</v>
@@ -10299,13 +10225,13 @@
         <v>29</v>
       </c>
       <c r="Q26" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="R26" t="s">
         <v>20</v>
       </c>
       <c r="S26" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="U26" t="s">
         <v>20</v>
@@ -10316,7 +10242,7 @@
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="B27" t="s">
         <v>8</v>
@@ -10337,10 +10263,10 @@
         <v>20</v>
       </c>
       <c r="H27" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I27" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J27" t="s">
         <v>29</v>
@@ -10349,13 +10275,13 @@
         <v>63</v>
       </c>
       <c r="L27" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M27" t="s">
         <v>84</v>
       </c>
       <c r="N27" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O27" t="s">
         <v>20</v>
@@ -10364,13 +10290,13 @@
         <v>29</v>
       </c>
       <c r="Q27" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="R27" t="s">
         <v>20</v>
       </c>
       <c r="S27" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="U27" t="s">
         <v>20</v>
@@ -10381,7 +10307,7 @@
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="B28" t="s">
         <v>8</v>
@@ -10402,10 +10328,10 @@
         <v>20</v>
       </c>
       <c r="H28" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="I28" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J28" t="s">
         <v>29</v>
@@ -10414,7 +10340,7 @@
         <v>63</v>
       </c>
       <c r="L28" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="M28" t="s">
         <v>20</v>
@@ -10435,7 +10361,7 @@
         <v>20</v>
       </c>
       <c r="S28" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="U28" t="s">
         <v>20</v>
@@ -10446,7 +10372,7 @@
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B29" t="s">
         <v>8</v>
@@ -10467,10 +10393,10 @@
         <v>20</v>
       </c>
       <c r="H29" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="I29" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J29" t="s">
         <v>29</v>
@@ -10494,13 +10420,13 @@
         <v>29</v>
       </c>
       <c r="Q29" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="R29" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="S29" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="U29" t="s">
         <v>20</v>
@@ -10511,7 +10437,7 @@
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B30" t="s">
         <v>8</v>
@@ -10532,10 +10458,10 @@
         <v>20</v>
       </c>
       <c r="H30" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="I30" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="J30" t="s">
         <v>29</v>
@@ -10544,7 +10470,7 @@
         <v>63</v>
       </c>
       <c r="L30" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M30" t="s">
         <v>84</v>
@@ -10565,7 +10491,7 @@
         <v>20</v>
       </c>
       <c r="S30" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="U30" t="s">
         <v>20</v>
@@ -10576,7 +10502,7 @@
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="B31" t="s">
         <v>8</v>
@@ -10597,7 +10523,7 @@
         <v>20</v>
       </c>
       <c r="H31" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="I31" t="s">
         <v>20</v>
@@ -10609,13 +10535,13 @@
         <v>20</v>
       </c>
       <c r="L31" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M31" t="s">
         <v>20</v>
       </c>
       <c r="N31" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="O31" t="s">
         <v>20</v>
@@ -10624,13 +10550,13 @@
         <v>29</v>
       </c>
       <c r="Q31" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="R31" t="s">
         <v>20</v>
       </c>
       <c r="S31" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="U31" t="s">
         <v>20</v>
@@ -10641,7 +10567,7 @@
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B32" t="s">
         <v>8</v>
@@ -10662,10 +10588,10 @@
         <v>20</v>
       </c>
       <c r="H32" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I32" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J32" t="s">
         <v>29</v>
@@ -10674,13 +10600,13 @@
         <v>63</v>
       </c>
       <c r="L32" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M32" t="s">
         <v>84</v>
       </c>
       <c r="N32" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O32" t="s">
         <v>20</v>
@@ -10689,13 +10615,13 @@
         <v>29</v>
       </c>
       <c r="Q32" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="R32" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="S32" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="U32" t="s">
         <v>20</v>
@@ -10706,7 +10632,7 @@
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="B33" t="s">
         <v>41</v>
@@ -10724,10 +10650,10 @@
         <v>20</v>
       </c>
       <c r="G33" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H33" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="I33" t="s">
         <v>33</v>
@@ -10745,7 +10671,7 @@
         <v>84</v>
       </c>
       <c r="N33" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O33" t="s">
         <v>20</v>
@@ -10754,16 +10680,16 @@
         <v>51</v>
       </c>
       <c r="Q33" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="R33" t="s">
         <v>20</v>
       </c>
       <c r="S33" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="U33" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="V33">
         <v>6</v>
@@ -10771,7 +10697,7 @@
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="B34" t="s">
         <v>41</v>
@@ -10792,7 +10718,7 @@
         <v>20</v>
       </c>
       <c r="H34" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="I34" t="s">
         <v>33</v>
@@ -10810,19 +10736,19 @@
         <v>84</v>
       </c>
       <c r="N34" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="O34" t="s">
         <v>20</v>
       </c>
       <c r="P34" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="Q34" t="s">
         <v>20</v>
       </c>
       <c r="R34" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="S34" t="s">
         <v>20</v>
@@ -10836,7 +10762,7 @@
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="B35" t="s">
         <v>8</v>
@@ -10854,46 +10780,46 @@
         <v>46</v>
       </c>
       <c r="G35" t="s">
+        <v>549</v>
+      </c>
+      <c r="H35" t="s">
+        <v>514</v>
+      </c>
+      <c r="I35" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35" t="s">
+        <v>29</v>
+      </c>
+      <c r="K35" t="s">
+        <v>550</v>
+      </c>
+      <c r="L35" t="s">
+        <v>30</v>
+      </c>
+      <c r="M35" t="s">
+        <v>208</v>
+      </c>
+      <c r="N35" t="s">
+        <v>208</v>
+      </c>
+      <c r="O35" t="s">
+        <v>20</v>
+      </c>
+      <c r="P35" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>551</v>
+      </c>
+      <c r="R35" t="s">
+        <v>552</v>
+      </c>
+      <c r="S35" t="s">
+        <v>20</v>
+      </c>
+      <c r="U35" t="s">
         <v>553</v>
-      </c>
-      <c r="H35" t="s">
-        <v>518</v>
-      </c>
-      <c r="I35" t="s">
-        <v>20</v>
-      </c>
-      <c r="J35" t="s">
-        <v>29</v>
-      </c>
-      <c r="K35" t="s">
-        <v>554</v>
-      </c>
-      <c r="L35" t="s">
-        <v>30</v>
-      </c>
-      <c r="M35" t="s">
-        <v>209</v>
-      </c>
-      <c r="N35" t="s">
-        <v>209</v>
-      </c>
-      <c r="O35" t="s">
-        <v>20</v>
-      </c>
-      <c r="P35" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>555</v>
-      </c>
-      <c r="R35" t="s">
-        <v>556</v>
-      </c>
-      <c r="S35" t="s">
-        <v>20</v>
-      </c>
-      <c r="U35" t="s">
-        <v>557</v>
       </c>
       <c r="V35">
         <v>8</v>
@@ -10901,7 +10827,7 @@
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="B36" t="s">
         <v>8</v>
@@ -10949,13 +10875,13 @@
         <v>29</v>
       </c>
       <c r="Q36" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="R36" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="S36" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="U36">
         <v>3212598389</v>
@@ -10966,7 +10892,7 @@
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="B37" t="s">
         <v>8</v>
@@ -10987,7 +10913,7 @@
         <v>20</v>
       </c>
       <c r="H37" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="I37" t="s">
         <v>20</v>
@@ -10999,13 +10925,13 @@
         <v>63</v>
       </c>
       <c r="L37" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M37" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="N37" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="O37" t="s">
         <v>20</v>
@@ -11017,10 +10943,10 @@
         <v>20</v>
       </c>
       <c r="R37" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="S37" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="U37">
         <v>3212598389</v>
@@ -11031,7 +10957,7 @@
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="B38" t="s">
         <v>8</v>
@@ -11052,7 +10978,7 @@
         <v>20</v>
       </c>
       <c r="H38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I38" t="s">
         <v>33</v>
@@ -11064,7 +10990,7 @@
         <v>63</v>
       </c>
       <c r="L38" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M38" t="s">
         <v>84</v>
@@ -11079,13 +11005,13 @@
         <v>29</v>
       </c>
       <c r="Q38" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="R38" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="S38" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="U38">
         <v>3212598389</v>
@@ -11096,7 +11022,7 @@
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="B39" t="s">
         <v>8</v>
@@ -11117,25 +11043,25 @@
         <v>20</v>
       </c>
       <c r="H39" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I39" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J39" t="s">
         <v>29</v>
       </c>
       <c r="K39" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L39" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M39" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="N39" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O39" t="s">
         <v>20</v>
@@ -11144,13 +11070,13 @@
         <v>29</v>
       </c>
       <c r="Q39" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="R39" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="S39" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="U39">
         <v>3212598389</v>
@@ -11161,7 +11087,7 @@
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="B40" t="s">
         <v>8</v>
@@ -11182,7 +11108,7 @@
         <v>20</v>
       </c>
       <c r="H40" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="I40" t="s">
         <v>33</v>
@@ -11191,16 +11117,16 @@
         <v>29</v>
       </c>
       <c r="K40" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L40" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M40" t="s">
         <v>84</v>
       </c>
       <c r="N40" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="O40" t="s">
         <v>20</v>
@@ -11209,13 +11135,13 @@
         <v>29</v>
       </c>
       <c r="Q40" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="R40" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="S40" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="U40">
         <v>3212598389</v>
@@ -11226,7 +11152,7 @@
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="B41" t="s">
         <v>8</v>
@@ -11247,7 +11173,7 @@
         <v>20</v>
       </c>
       <c r="H41" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="I41" t="s">
         <v>33</v>
@@ -11262,10 +11188,10 @@
         <v>30</v>
       </c>
       <c r="M41" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="N41" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="O41" t="s">
         <v>20</v>
@@ -11274,13 +11200,13 @@
         <v>29</v>
       </c>
       <c r="Q41" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="R41" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="S41" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="U41">
         <v>3212598389</v>
@@ -11291,7 +11217,7 @@
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="B42" t="s">
         <v>41</v>
@@ -11312,7 +11238,7 @@
         <v>20</v>
       </c>
       <c r="H42" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I42" t="s">
         <v>33</v>
@@ -11339,10 +11265,10 @@
         <v>29</v>
       </c>
       <c r="Q42" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="R42" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="S42" t="s">
         <v>20</v>
@@ -11356,26 +11282,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="G1:Q1"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:E2"/>
+    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
     <mergeCell ref="R1:R3"/>
     <mergeCell ref="S1:S3"/>
     <mergeCell ref="T1:T3"/>
     <mergeCell ref="U1:U3"/>
     <mergeCell ref="V1:V3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:E2"/>
-    <mergeCell ref="F1:F3"/>
-    <mergeCell ref="G1:Q1"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="P2:P3"/>
-    <mergeCell ref="Q2:Q3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11396,13 +11322,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C1" t="s">
         <v>392</v>
       </c>
-      <c r="C1" t="s">
-        <v>393</v>
-      </c>
       <c r="D1" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -11410,10 +11336,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C2" t="s">
         <v>394</v>
-      </c>
-      <c r="C2" t="s">
-        <v>395</v>
       </c>
       <c r="D2" t="s">
         <v>35</v>
@@ -11424,10 +11350,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D3" t="s">
         <v>35</v>
@@ -11438,10 +11364,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C4" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="D4" t="s">
         <v>35</v>
@@ -11452,10 +11378,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="C5" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="D5" t="s">
         <v>35</v>
@@ -11466,10 +11392,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="C6" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="D6" t="s">
         <v>35</v>
@@ -11480,10 +11406,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>520</v>
+      </c>
+      <c r="C7" t="s">
         <v>524</v>
-      </c>
-      <c r="C7" t="s">
-        <v>528</v>
       </c>
       <c r="D7" t="s">
         <v>35</v>
@@ -11494,10 +11420,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>521</v>
+      </c>
+      <c r="C8" t="s">
         <v>525</v>
-      </c>
-      <c r="C8" t="s">
-        <v>529</v>
       </c>
       <c r="D8" t="s">
         <v>35</v>
@@ -11508,10 +11434,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="C9" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="D9" t="s">
         <v>35</v>
@@ -11522,13 +11448,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="C10" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="D10" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -11536,13 +11462,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="C11" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="D11" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -11550,13 +11476,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C12" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="D12" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -11564,13 +11490,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="C13" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="D13" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -11578,10 +11504,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="C14" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="D14" t="s">
         <v>35</v>
@@ -11592,10 +11518,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C15" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="D15" t="s">
         <v>35</v>
@@ -11606,10 +11532,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="C16" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="D16" t="s">
         <v>35</v>
@@ -11620,13 +11546,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="C17" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="D17" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Base de Datos de Masctoas.xlsx
+++ b/docs/Base de Datos de Masctoas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30411"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f5f906da8c23dd95/Desktop/Terremoto Mascotas/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3502" documentId="11_F25DC773A252ABDACC10485489D862385BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06DF067F-C0D0-40FE-B307-D64772C88131}"/>
+  <xr:revisionPtr revIDLastSave="3503" documentId="11_F25DC773A252ABDACC10485489D862385BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C866F318-2CE6-41C5-BE22-FA7CA74F75FB}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="24" yWindow="0" windowWidth="23016" windowHeight="12216" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Observadas" sheetId="1" r:id="rId1"/>
@@ -3062,7 +3062,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3092,6 +3092,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -3110,26 +3123,23 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3152,27 +3162,15 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3192,6 +3190,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3490,7 +3492,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F944E3DE-FE9C-4E6E-B46E-81628292EFC9}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:V101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3509,109 +3510,109 @@
     <col min="18" max="18" width="72" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="17.21875" hidden="1" customWidth="1"/>
     <col min="20" max="20" width="10" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="16.6640625" style="41" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19" t="s">
+      <c r="E1" s="13"/>
+      <c r="F1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19" t="s">
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="21" t="s">
+      <c r="S1" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="19" t="s">
+      <c r="T1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="U1" s="39" t="s">
+      <c r="U1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="V1" s="20" t="s">
+      <c r="V1" s="15" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="2" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="22" t="s">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20" t="s">
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="L2" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="20" t="s">
+      <c r="M2" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="N2" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="20" t="s">
+      <c r="O2" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="P2" s="20" t="s">
+      <c r="P2" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="Q2" s="20" t="s">
+      <c r="Q2" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="19"/>
-      <c r="S2" s="21"/>
-      <c r="T2" s="19"/>
-      <c r="U2" s="19"/>
-      <c r="V2" s="20"/>
-    </row>
-    <row r="3" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="13"/>
+      <c r="V2" s="15"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
       <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="19"/>
-      <c r="G3" s="22"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="14"/>
       <c r="H3" s="1" t="s">
         <v>28</v>
       </c>
@@ -3621,20 +3622,20 @@
       <c r="J3" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
-      <c r="O3" s="20"/>
-      <c r="P3" s="20"/>
-      <c r="Q3" s="20"/>
-      <c r="R3" s="19"/>
-      <c r="S3" s="21"/>
-      <c r="T3" s="19"/>
-      <c r="U3" s="19"/>
-      <c r="V3" s="20"/>
-    </row>
-    <row r="4" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="17"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="13"/>
+      <c r="V3" s="15"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>68</v>
       </c>
@@ -3700,7 +3701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>69</v>
       </c>
@@ -3766,7 +3767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>70</v>
       </c>
@@ -3832,7 +3833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>71</v>
       </c>
@@ -3898,7 +3899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>72</v>
       </c>
@@ -3964,7 +3965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>73</v>
       </c>
@@ -4030,7 +4031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>78</v>
       </c>
@@ -4096,7 +4097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>86</v>
       </c>
@@ -4162,7 +4163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>87</v>
       </c>
@@ -4228,7 +4229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>88</v>
       </c>
@@ -4353,14 +4354,14 @@
       <c r="T14" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="U14" s="40">
+      <c r="U14" s="4">
         <v>3022853805</v>
       </c>
       <c r="V14" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>90</v>
       </c>
@@ -4426,7 +4427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>91</v>
       </c>
@@ -4492,7 +4493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>92</v>
       </c>
@@ -4558,7 +4559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>93</v>
       </c>
@@ -4624,7 +4625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>94</v>
       </c>
@@ -4690,7 +4691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>95</v>
       </c>
@@ -4756,7 +4757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>96</v>
       </c>
@@ -4822,7 +4823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>97</v>
       </c>
@@ -4888,7 +4889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>98</v>
       </c>
@@ -4954,7 +4955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>99</v>
       </c>
@@ -5020,7 +5021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>100</v>
       </c>
@@ -5086,7 +5087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>101</v>
       </c>
@@ -5152,7 +5153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>102</v>
       </c>
@@ -5218,7 +5219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>103</v>
       </c>
@@ -5284,7 +5285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>104</v>
       </c>
@@ -5350,7 +5351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>105</v>
       </c>
@@ -5416,7 +5417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>106</v>
       </c>
@@ -5482,7 +5483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>107</v>
       </c>
@@ -5548,7 +5549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>108</v>
       </c>
@@ -5614,7 +5615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>109</v>
       </c>
@@ -5680,7 +5681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
         <v>110</v>
       </c>
@@ -5746,7 +5747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>111</v>
       </c>
@@ -5812,7 +5813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
         <v>112</v>
       </c>
@@ -5878,7 +5879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
         <v>113</v>
       </c>
@@ -5944,7 +5945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>114</v>
       </c>
@@ -6010,7 +6011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>115</v>
       </c>
@@ -6076,7 +6077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>116</v>
       </c>
@@ -6142,7 +6143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>117</v>
       </c>
@@ -6208,7 +6209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>118</v>
       </c>
@@ -6274,7 +6275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
         <v>119</v>
       </c>
@@ -6340,7 +6341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
         <v>120</v>
       </c>
@@ -6406,7 +6407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
         <v>121</v>
       </c>
@@ -6472,7 +6473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
         <v>122</v>
       </c>
@@ -6538,7 +6539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
         <v>123</v>
       </c>
@@ -6604,7 +6605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
         <v>124</v>
       </c>
@@ -6670,7 +6671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
         <v>125</v>
       </c>
@@ -6736,7 +6737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
         <v>126</v>
       </c>
@@ -6802,7 +6803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
         <v>127</v>
       </c>
@@ -6868,7 +6869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
         <v>128</v>
       </c>
@@ -6934,7 +6935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
         <v>129</v>
       </c>
@@ -7000,7 +7001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
         <v>130</v>
       </c>
@@ -7066,7 +7067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
         <v>131</v>
       </c>
@@ -7132,7 +7133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
         <v>132</v>
       </c>
@@ -7198,7 +7199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
         <v>133</v>
       </c>
@@ -7264,7 +7265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
         <v>134</v>
       </c>
@@ -7330,7 +7331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
         <v>135</v>
       </c>
@@ -7396,7 +7397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>136</v>
       </c>
@@ -7462,7 +7463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>137</v>
       </c>
@@ -7528,7 +7529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
         <v>138</v>
       </c>
@@ -7594,7 +7595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A64" s="7" t="s">
         <v>139</v>
       </c>
@@ -7660,7 +7661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
         <v>140</v>
       </c>
@@ -7726,7 +7727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
         <v>141</v>
       </c>
@@ -7792,7 +7793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
         <v>142</v>
       </c>
@@ -7858,7 +7859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
         <v>143</v>
       </c>
@@ -7924,7 +7925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
         <v>144</v>
       </c>
@@ -7990,7 +7991,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
         <v>145</v>
       </c>
@@ -8056,7 +8057,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:22" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
         <v>146</v>
       </c>
@@ -8120,7 +8121,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A72" s="7" t="s">
         <v>147</v>
       </c>
@@ -8186,7 +8187,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A73" s="7" t="s">
         <v>148</v>
       </c>
@@ -8252,7 +8253,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A74" s="7" t="s">
         <v>149</v>
       </c>
@@ -8318,7 +8319,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A75" s="7" t="s">
         <v>469</v>
       </c>
@@ -8384,7 +8385,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A76" s="7" t="s">
         <v>497</v>
       </c>
@@ -8450,7 +8451,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A77" s="7" t="s">
         <v>498</v>
       </c>
@@ -8516,7 +8517,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A78" s="7" t="s">
         <v>499</v>
       </c>
@@ -8582,7 +8583,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A79" s="7" t="s">
         <v>500</v>
       </c>
@@ -8648,7 +8649,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="80" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A80" s="7" t="s">
         <v>501</v>
       </c>
@@ -8714,7 +8715,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="81" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A81" s="7" t="s">
         <v>502</v>
       </c>
@@ -8780,7 +8781,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A82" s="7" t="s">
         <v>503</v>
       </c>
@@ -8844,7 +8845,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="83" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A83" s="7" t="s">
         <v>504</v>
       </c>
@@ -8910,7 +8911,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="84" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A84" s="7" t="s">
         <v>505</v>
       </c>
@@ -8976,7 +8977,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="85" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A85" s="7" t="s">
         <v>506</v>
       </c>
@@ -9042,7 +9043,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="86" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A86" s="7" t="s">
         <v>507</v>
       </c>
@@ -9108,7 +9109,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="87" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A87" s="7" t="s">
         <v>565</v>
       </c>
@@ -9174,7 +9175,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="88" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A88" s="7" t="s">
         <v>566</v>
       </c>
@@ -9240,7 +9241,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="89" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A89" s="7" t="s">
         <v>567</v>
       </c>
@@ -9306,7 +9307,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="90" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A90" s="7" t="s">
         <v>568</v>
       </c>
@@ -9372,7 +9373,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="91" spans="1:22" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A91" s="7" t="s">
         <v>569</v>
       </c>
@@ -9424,7 +9425,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A92" s="7" t="s">
         <v>590</v>
       </c>
@@ -9474,7 +9475,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A93" s="7" t="s">
         <v>593</v>
       </c>
@@ -9524,7 +9525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A94" s="7" t="s">
         <v>597</v>
       </c>
@@ -9568,7 +9569,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A95" s="7" t="s">
         <v>601</v>
       </c>
@@ -9612,7 +9613,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A96" s="7" t="s">
         <v>605</v>
       </c>
@@ -9656,7 +9657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:22" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A97" s="7" t="s">
         <v>609</v>
       </c>
@@ -9698,7 +9699,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A98" s="7" t="s">
         <v>615</v>
       </c>
@@ -9742,7 +9743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A99" s="7" t="s">
         <v>622</v>
       </c>
@@ -9786,7 +9787,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A100" s="7" t="s">
         <v>626</v>
       </c>
@@ -9867,7 +9868,7 @@
       </c>
       <c r="S101" s="4"/>
       <c r="T101" s="4"/>
-      <c r="U101" s="40">
+      <c r="U101" s="4">
         <v>3154975605</v>
       </c>
       <c r="V101" s="7">
@@ -9876,11 +9877,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:V101" xr:uid="{F944E3DE-FE9C-4E6E-B46E-81628292EFC9}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Candy"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="3" showButton="0"/>
     <filterColumn colId="6" showButton="0"/>
     <filterColumn colId="7" showButton="0"/>
@@ -9894,18 +9890,6 @@
     <filterColumn colId="15" showButton="0"/>
   </autoFilter>
   <mergeCells count="20">
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:E2"/>
-    <mergeCell ref="F1:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="G1:Q1"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="Q2:Q3"/>
     <mergeCell ref="U1:U3"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="M2:M3"/>
@@ -9914,6 +9898,18 @@
     <mergeCell ref="O2:O3"/>
     <mergeCell ref="R1:R3"/>
     <mergeCell ref="T1:T3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="G1:Q1"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:E2"/>
+    <mergeCell ref="F1:F3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9934,70 +9930,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="13" t="s">
         <v>904</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="18" t="s">
         <v>908</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="18" t="s">
         <v>909</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="18" t="s">
         <v>910</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="21" t="s">
         <v>905</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="18" t="s">
         <v>902</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="18" t="s">
         <v>903</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="18" t="s">
         <v>914</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="18" t="s">
         <v>915</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="18" t="s">
         <v>906</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="L1" s="21" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="17"/>
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="22"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="18"/>
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="23"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -10217,105 +10213,105 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="26" t="s">
+      <c r="E1" s="34"/>
+      <c r="F1" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="23" t="s">
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="37" t="s">
         <v>427</v>
       </c>
-      <c r="S1" s="26" t="s">
+      <c r="S1" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="T1" s="23" t="s">
+      <c r="T1" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="U1" s="26" t="s">
+      <c r="U1" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="V1" s="16" t="s">
+      <c r="V1" s="21" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" s="27"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="13" t="s">
+      <c r="A2" s="31"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="36" t="s">
+      <c r="H2" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="37"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="16" t="s">
+      <c r="I2" s="28"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="L2" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="M2" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="N2" s="16" t="s">
+      <c r="N2" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="16" t="s">
+      <c r="O2" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="P2" s="16" t="s">
+      <c r="P2" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="Q2" s="16" t="s">
+      <c r="Q2" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="24"/>
-      <c r="S2" s="27"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="27"/>
-      <c r="V2" s="17"/>
+      <c r="R2" s="38"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="38"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="22"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A3" s="28"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
       <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="28"/>
-      <c r="G3" s="15"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="20"/>
       <c r="H3" s="1" t="s">
         <v>28</v>
       </c>
@@ -10325,18 +10321,18 @@
       <c r="J3" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
-      <c r="N3" s="18"/>
-      <c r="O3" s="18"/>
-      <c r="P3" s="18"/>
-      <c r="Q3" s="18"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="28"/>
-      <c r="V3" s="18"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="32"/>
+      <c r="T3" s="39"/>
+      <c r="U3" s="32"/>
+      <c r="V3" s="23"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -17300,6 +17296,16 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="R1:R3"/>
+    <mergeCell ref="S1:S3"/>
+    <mergeCell ref="T1:T3"/>
+    <mergeCell ref="U1:U3"/>
+    <mergeCell ref="V1:V3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:E2"/>
+    <mergeCell ref="F1:F3"/>
     <mergeCell ref="G1:Q1"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="O2:O3"/>
@@ -17310,16 +17316,6 @@
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="L2:L3"/>
     <mergeCell ref="M2:M3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:E2"/>
-    <mergeCell ref="F1:F3"/>
-    <mergeCell ref="R1:R3"/>
-    <mergeCell ref="S1:S3"/>
-    <mergeCell ref="T1:T3"/>
-    <mergeCell ref="U1:U3"/>
-    <mergeCell ref="V1:V3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
